--- a/Pruebas calificadas/COLEGIO-ALEJANDRO-OBREGON-(IED)-302_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ALEJANDRO-OBREGON-(IED)-302_Ajustado_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -942,11 +938,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -954,7 +946,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1145,11 +1137,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -1157,7 +1145,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1348,11 +1336,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -1360,7 +1344,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1551,11 +1535,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -1563,7 +1543,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1754,11 +1734,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -1766,7 +1742,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1957,11 +1933,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -1969,7 +1941,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2160,11 +2132,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -2172,7 +2140,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2363,11 +2331,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -2375,7 +2339,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2566,11 +2530,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -2578,7 +2538,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2769,11 +2729,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -2781,7 +2737,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2972,11 +2928,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -2984,7 +2936,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3175,11 +3127,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -3187,7 +3135,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3378,11 +3326,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -3390,7 +3334,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3581,11 +3525,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -3593,7 +3533,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3784,11 +3724,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -3796,7 +3732,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3987,11 +3923,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -3999,7 +3931,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4190,11 +4122,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -4202,7 +4130,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4393,11 +4321,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -4405,7 +4329,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4592,11 +4516,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -4604,7 +4524,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4795,11 +4715,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -4807,7 +4723,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4998,11 +4914,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -5010,7 +4922,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5201,11 +5113,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -5213,7 +5121,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5404,11 +5312,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -5416,7 +5320,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5607,11 +5511,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -5619,7 +5519,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5810,11 +5710,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -5822,7 +5718,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6013,11 +5909,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -6025,7 +5917,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6212,11 +6104,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -6224,7 +6112,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6415,11 +6303,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -6427,7 +6311,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6618,11 +6502,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -6630,7 +6510,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6821,11 +6701,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -6833,7 +6709,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7024,11 +6900,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -7036,7 +6908,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7227,11 +7099,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -7239,7 +7107,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7430,11 +7298,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -7442,7 +7306,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7633,11 +7497,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -7645,7 +7505,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7836,11 +7696,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -7848,7 +7704,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8035,11 +7891,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -8047,7 +7899,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8238,11 +8090,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -8250,7 +8098,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8441,11 +8289,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -8453,7 +8297,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8644,11 +8488,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -8656,7 +8496,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8847,11 +8687,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -8859,7 +8695,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9050,11 +8886,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -9062,7 +8894,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9253,11 +9085,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -9265,7 +9093,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9456,11 +9284,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -9468,7 +9292,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9659,11 +9483,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -9671,7 +9491,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9862,11 +9682,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -9874,7 +9690,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10065,11 +9881,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -10077,7 +9889,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10268,11 +10080,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -10280,7 +10088,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10471,11 +10279,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -10483,7 +10287,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10674,11 +10478,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -10686,7 +10486,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10877,11 +10677,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -10889,7 +10685,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11080,11 +10876,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -11092,7 +10884,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11283,11 +11075,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -11295,7 +11083,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11486,11 +11274,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -11498,7 +11282,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11689,11 +11473,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -11701,7 +11481,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11892,11 +11672,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -11904,7 +11680,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12095,11 +11871,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -12107,7 +11879,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12298,11 +12070,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001015172</t>
@@ -12310,7 +12078,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ALEJANDRO OBREGON (IED)</t>
+          <t>COLEGIO ALEJANDRO OBREGON</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
